--- a/trading_signals/risk_management/risk_workbook_20260605_032615.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260605_032615.xlsx
@@ -175,13 +175,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -194,9 +197,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-04  ·  Generated 2026-06-05T03:27:22  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-04  ·  Generated 2026-06-10T09:47:35  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1117239.48</v>
+        <v>1111711.73</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2.421</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1.706</v>
+        <v>1.715</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>30.98</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.87</v>
+        <v>1.911</v>
       </c>
     </row>
     <row r="12">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.9611</v>
+        <v>0.9617</v>
       </c>
     </row>
     <row r="13">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -840,7 +840,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>8.63 / 4.31</t>
+          <t>9.23 / 4.62</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2.421</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BWA (32.53% NAV)</t>
+          <t>BWA (32.69% NAV)</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>30.98</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1043,7 @@
       <c r="B13" s="13" t="n">
         <v>4849.71</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>13.52</v>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       <c r="B15" s="13" t="n">
         <v>3174.89</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>8.85</v>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       <c r="B17" s="13" t="n">
         <v>2093.34</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>5.84</v>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       <c r="B19" s="13" t="n">
         <v>1889.21</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>5.27</v>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       <c r="B21" s="13" t="n">
         <v>1692.57</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>4.72</v>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       <c r="B23" s="13" t="n">
         <v>1590.19</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>4.43</v>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       <c r="B25" s="13" t="n">
         <v>763.01</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>2.13</v>
       </c>
     </row>
@@ -1308,18 +1308,18 @@
           <t>MTD</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>CI/MTD</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="15" t="n">
         <v>82</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>225318</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
           <t>JKHY</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>ODFL/JKHY</t>
         </is>
@@ -1361,7 +1361,7 @@
       <c r="D9" s="13" t="n">
         <v>1473525</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1392,18 +1392,18 @@
           <t>REGN</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="15" t="n">
         <v>23</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>1025882</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>KLAC/LOW</t>
         </is>
@@ -1443,9 +1443,9 @@
         <v>382</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>3121368</v>
-      </c>
-      <c r="E13" s="16" t="n">
+        <v>3121374</v>
+      </c>
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
           <t>VLTO</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>FFIV/VLTO</t>
         </is>
@@ -1487,7 +1487,7 @@
       <c r="D15" s="13" t="n">
         <v>2530621</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
           <t>BSX</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>LRCX/BSX</t>
         </is>
@@ -1527,9 +1527,9 @@
         <v>1706</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>18473203</v>
-      </c>
-      <c r="E17" s="16" t="n">
+        <v>18473704</v>
+      </c>
+      <c r="E17" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
           <t>RMD</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>LRCX/RMD</t>
         </is>
@@ -1571,7 +1571,7 @@
       <c r="D19" s="13" t="n">
         <v>1540432</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1648,11 +1648,11 @@
           <t>SPY -5%</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
-        <v>-95300.53</v>
-      </c>
-      <c r="C4" s="21" t="n">
-        <v>-8.529999999999999</v>
+      <c r="B4" s="19" t="n">
+        <v>-95329.28</v>
+      </c>
+      <c r="C4" s="22" t="n">
+        <v>-8.58</v>
       </c>
     </row>
     <row r="5">
@@ -1661,11 +1661,11 @@
           <t>SPY -10%</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
-        <v>-190601.06</v>
+      <c r="B5" s="18" t="n">
+        <v>-190658.56</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>-17.06</v>
+        <v>-17.15</v>
       </c>
     </row>
     <row r="6">
@@ -1674,11 +1674,11 @@
           <t>VIX +10pt</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
-        <v>-95300.53</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>-8.529999999999999</v>
+      <c r="B6" s="19" t="n">
+        <v>-95329.28</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>-8.58</v>
       </c>
     </row>
     <row r="7">
@@ -1687,11 +1687,11 @@
           <t>Top sector -10%</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="18" t="n">
         <v>-85782.05</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>-7.68</v>
+        <v>-7.72</v>
       </c>
     </row>
   </sheetData>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="C4" s="30" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>3</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>4.36</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>3</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>32.53</v>
+        <v>32.69</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>25.96</v>
+        <v>26.08</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1915,28 +1915,28 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>single_name_gross</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>STLD</t>
         </is>
       </c>
-      <c r="C10" s="34" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="D10" s="34" t="n">
+      <c r="C10" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="34" t="n">
+      <c r="E10" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="34" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="D13" s="32" t="n">
         <v>0.3</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="C14" s="34" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="D14" s="34" t="n">
         <v>3</v>
@@ -2186,17 +2186,17 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>CI/MTD</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>short</t>
         </is>
@@ -2207,18 +2207,18 @@
       <c r="F4" s="13" t="n">
         <v>280.68</v>
       </c>
-      <c r="G4" s="22" t="n">
+      <c r="G4" s="18" t="n">
         <v>-87572.16</v>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>health</t>
         </is>
       </c>
-      <c r="I4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="I4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>vol_agnostic</t>
         </is>
@@ -2274,17 +2274,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>ODFL/JKHY</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>ODFL</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2298,15 +2298,15 @@
       <c r="G6" s="13" t="n">
         <v>31426.56</v>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="I6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="I6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>conservative</t>
         </is>
@@ -2339,7 +2339,7 @@
       <c r="F7" s="4" t="n">
         <v>130.73</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="19" t="n">
         <v>-24969.43</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -2362,17 +2362,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>KLAC</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2386,15 +2386,15 @@
       <c r="G8" s="13" t="n">
         <v>142783.7</v>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="I8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>beta_neutral_long_term</t>
         </is>
@@ -2427,7 +2427,7 @@
       <c r="F9" s="4" t="n">
         <v>628.73</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="19" t="n">
         <v>-14460.79</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -2450,17 +2450,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>KLAC/LOW</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>KLAC</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2474,15 +2474,15 @@
       <c r="G10" s="13" t="n">
         <v>89506.2</v>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I10" s="16" t="n">
+      <c r="I10" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>aggressive</t>
         </is>
@@ -2515,7 +2515,7 @@
       <c r="F11" s="4" t="n">
         <v>207.53</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="19" t="n">
         <v>-79276.46000000001</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -2538,17 +2538,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>FFIV/VLTO</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>FFIV</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2562,15 +2562,15 @@
       <c r="G12" s="13" t="n">
         <v>174089.16</v>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="I12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>long_term_tilt</t>
         </is>
@@ -2603,7 +2603,7 @@
       <c r="F13" s="11" t="n">
         <v>84.73999999999999</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>-56352.1</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -2626,17 +2626,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>LRCX/BSX</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>LRCX</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2650,15 +2650,15 @@
       <c r="G14" s="13" t="n">
         <v>144992.71</v>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="I14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>aggressive</t>
         </is>
@@ -2691,7 +2691,7 @@
       <c r="F15" s="11" t="n">
         <v>48.85</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>-83338.10000000001</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -2714,17 +2714,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>LRCX/RMD</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>LRCX</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2738,15 +2738,15 @@
       <c r="G16" s="13" t="n">
         <v>144992.71</v>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I16" s="16" t="n">
+      <c r="I16" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>fast_rebalance</t>
         </is>
@@ -2779,7 +2779,7 @@
       <c r="F17" s="4" t="n">
         <v>194.32</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>-55964.16</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2802,17 +2802,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>CSCO/CAG</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>CSCO</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2826,15 +2826,15 @@
       <c r="G18" s="13" t="n">
         <v>118560</v>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="I18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>fast_strict</t>
         </is>
@@ -2867,7 +2867,7 @@
       <c r="F19" s="11" t="n">
         <v>12.68</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="19" t="n">
         <v>-52457.16</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2890,17 +2890,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>NUE/INTU</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>NUE</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2914,15 +2914,15 @@
       <c r="G20" s="13" t="n">
         <v>86290.12</v>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="I20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>conservative</t>
         </is>
@@ -2955,7 +2955,7 @@
       <c r="F21" s="4" t="n">
         <v>301.98</v>
       </c>
-      <c r="G21" s="18" t="n">
+      <c r="G21" s="19" t="n">
         <v>-24762.36</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2978,17 +2978,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>CSCO/REGN</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>CSCO</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3002,15 +3002,15 @@
       <c r="G22" s="13" t="n">
         <v>118560</v>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="I22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>monthly_aligned_windows</t>
         </is>
@@ -3043,7 +3043,7 @@
       <c r="F23" s="4" t="n">
         <v>628.73</v>
       </c>
-      <c r="G23" s="18" t="n">
+      <c r="G23" s="19" t="n">
         <v>-55956.97</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -3066,17 +3066,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>NUE/MKTX</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>NUE</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3090,15 +3090,15 @@
       <c r="G24" s="13" t="n">
         <v>86290.12</v>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="I24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
@@ -3131,7 +3131,7 @@
       <c r="F25" s="4" t="n">
         <v>120.62</v>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="G25" s="19" t="n">
         <v>-50901.64</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -3154,17 +3154,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>STLD/ISRG</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>STLD</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3178,15 +3178,15 @@
       <c r="G26" s="13" t="n">
         <v>138978.7</v>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I26" s="16" t="n">
+      <c r="I26" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J26" s="17" t="inlineStr">
         <is>
           <t>beta_neutral</t>
         </is>
@@ -3219,7 +3219,7 @@
       <c r="F27" s="4" t="n">
         <v>418.82</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="19" t="n">
         <v>-33086.78</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -3242,17 +3242,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>BWA/VLTO</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>BWA</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3260,21 +3260,21 @@
       <c r="E28" s="26" t="n">
         <v>2359</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="15" t="n">
         <v>77.03</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>181713.77</v>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="I28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="I28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
@@ -3307,7 +3307,7 @@
       <c r="F29" s="11" t="n">
         <v>84.73999999999999</v>
       </c>
-      <c r="G29" s="18" t="n">
+      <c r="G29" s="19" t="n">
         <v>-81435.14</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -3330,17 +3330,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>STLD/HII</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>STLD</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3354,15 +3354,15 @@
       <c r="G30" s="13" t="n">
         <v>138978.7</v>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="I30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
@@ -3395,7 +3395,7 @@
       <c r="F31" s="4" t="n">
         <v>294.53</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="G31" s="19" t="n">
         <v>-52426.34</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -3418,17 +3418,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>BWA/CME</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>BWA</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3436,21 +3436,21 @@
       <c r="E32" s="26" t="n">
         <v>2359</v>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="15" t="n">
         <v>77.03</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>181713.77</v>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="I32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="I32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
@@ -3483,7 +3483,7 @@
       <c r="F33" s="4" t="n">
         <v>256.06</v>
       </c>
-      <c r="G33" s="18" t="n">
+      <c r="G33" s="19" t="n">
         <v>-76305.88</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3576,7 +3576,7 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>CI/MTD</t>
         </is>
@@ -3587,15 +3587,15 @@
       <c r="D4" s="13" t="n">
         <v>184371.52</v>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>vol_agnostic</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>short</t>
         </is>
@@ -3638,7 +3638,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>KLAC/REGN</t>
         </is>
@@ -3649,15 +3649,15 @@
       <c r="D6" s="13" t="n">
         <v>157244.49</v>
       </c>
-      <c r="E6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>beta_neutral_long_term</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3700,7 +3700,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>FFIV/VLTO</t>
         </is>
@@ -3711,15 +3711,15 @@
       <c r="D8" s="13" t="n">
         <v>230441.26</v>
       </c>
-      <c r="E8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>long_term_tilt</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3762,7 +3762,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>LRCX/RMD</t>
         </is>
@@ -3773,15 +3773,15 @@
       <c r="D10" s="13" t="n">
         <v>200956.87</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>fast_rebalance</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3824,7 +3824,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>NUE/INTU</t>
         </is>
@@ -3835,15 +3835,15 @@
       <c r="D12" s="13" t="n">
         <v>111052.48</v>
       </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>conservative</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3886,7 +3886,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>NUE/MKTX</t>
         </is>
@@ -3897,15 +3897,15 @@
       <c r="D14" s="13" t="n">
         <v>137191.76</v>
       </c>
-      <c r="E14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3948,7 +3948,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>BWA/VLTO</t>
         </is>
@@ -3959,15 +3959,15 @@
       <c r="D16" s="13" t="n">
         <v>263148.91</v>
       </c>
-      <c r="E16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="E16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4010,7 +4010,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>BWA/CME</t>
         </is>
@@ -4021,15 +4021,15 @@
       <c r="D18" s="13" t="n">
         <v>258019.65</v>
       </c>
-      <c r="E18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4104,12 +4104,12 @@
           <t>T_1D</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -4138,12 +4138,12 @@
           <t>T_1M</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -4228,16 +4228,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>13.49</v>
+        <v>14.42</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-1.13</v>
+        <v>-0.65</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="21" t="n">
-        <v>-14.63</v>
+      <c r="E6" s="22" t="n">
+        <v>-15.08</v>
       </c>
     </row>
     <row r="7">
@@ -4246,17 +4246,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="D7" s="16" t="n">
+      <c r="B7" s="17" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>-0.76</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="8">
@@ -4266,16 +4266,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24.35</v>
+        <v>24.38</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="21" t="n">
-        <v>-20.85</v>
+      <c r="E8" s="22" t="n">
+        <v>-20.84</v>
       </c>
     </row>
     <row r="9">
@@ -4284,17 +4284,17 @@
           <t>AISS</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>83.94</v>
-      </c>
-      <c r="D9" s="16" t="n">
+      <c r="B9" s="17" t="n">
+        <v>47.76</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>85.73</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="E9" s="19" t="n">
-        <v>36.24</v>
+      <c r="E9" s="20" t="n">
+        <v>37.97</v>
       </c>
     </row>
     <row r="11">
@@ -4332,7 +4332,7 @@
           <t>LRCX/RMD</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>13.52</v>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
           <t>STLD/HII</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>8.85</v>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
           <t>KLAC/LOW</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>5.84</v>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
           <t>CSCO/CAG</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>5.27</v>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
           <t>BWA/CME</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>4.72</v>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
           <t>CI/MTD</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>4.43</v>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
           <t>BWA/VLTO</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>2.13</v>
       </c>
     </row>
@@ -4573,46 +4573,46 @@
           <t>COMBINED</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
-        <v>38.24</v>
+      <c r="B5" s="21" t="n">
+        <v>38.97</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>0.006 (t=0.07)</t>
+          <t>0.003 (t=0.04)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>-0.083 (t=-0.61)</t>
+          <t>-0.075 (t=-0.55)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>0.081 (t=0.67)</t>
+          <t>0.073 (t=0.6)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>0.093 (t=0.83)</t>
+          <t>0.094 (t=0.83)</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.101 (t=-0.57)</t>
+          <t>-0.111 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>-0.108 (t=-1.71)</t>
+          <t>-0.11 (t=-1.72)</t>
         </is>
       </c>
     </row>
@@ -4622,46 +4622,46 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>36.54</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E6" s="16" t="n">
+      <c r="B6" s="20" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="E6" s="17" t="n">
         <v>116</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>0.154 (t=0.83)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>-0.235 (t=-0.82)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>-0.026 (t=-0.1)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>0.333 (t=1.39)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>-0.247 (t=-0.66)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>-0.163 (t=-1.21)</t>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>0.056 (t=0.39)</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>-0.116 (t=-0.52)</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>-0.06 (t=-0.31)</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>0.241 (t=1.31)</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>-0.207 (t=-0.72)</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>-0.141 (t=-1.36)</t>
         </is>
       </c>
     </row>
@@ -4671,46 +4671,46 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
-        <v>44.53</v>
+      <c r="B7" s="21" t="n">
+        <v>28.62</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.026</v>
+        <v>0.036</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.204 (t=-0.82)</t>
+          <t>-0.069 (t=-0.42)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>0.16 (t=0.41)</t>
+          <t>-0.004 (t=-0.02)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.188 (t=0.55)</t>
+          <t>0.235 (t=1.04)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.229 (t=-0.71)</t>
+          <t>-0.103 (t=-0.49)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.077 (t=0.15)</t>
+          <t>0.022 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.034 (t=-0.19)</t>
+          <t>-0.065 (t=-0.55)</t>
         </is>
       </c>
     </row>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>4.104</v>
+        <v>3.742</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>36.98</v>
+        <v>32.777</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -4811,10 +4811,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1.785</v>
+        <v>1.693</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1.785</v>
+        <v>1.693</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -4826,26 +4826,26 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>-3.082</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>22.551</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="16" t="b">
+      <c r="B5" s="17" t="n">
+        <v>-0.406</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2.324</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>2.036</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>2.344</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>0.308</v>
+      <c r="F5" s="17" t="n">
+        <v>1.594</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>1.661</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0.067</v>
       </c>
     </row>
     <row r="6">
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5.161</v>
+        <v>5.37</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>39.486</v>
+        <v>49.703</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -4867,10 +4867,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4.125</v>
+        <v>3.745</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4.125</v>
+        <v>3.745</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -4935,31 +4935,31 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.87</v>
+        <v>1.911</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.9611</v>
+        <v>0.9617</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8.640000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>9.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>75.7</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>8.630000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>4.31</v>
+        <v>4.62</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>2.421</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="10">
@@ -4968,32 +4968,32 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>0.6642</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>10.81</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>0.342</v>
+      <c r="B10" s="17" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>0.8473000000000001</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>377</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="11">
@@ -5003,13 +5003,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1.564</v>
+        <v>1.357</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9026</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.04</v>
@@ -5021,13 +5021,13 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>4.361</v>
+        <v>4.703</v>
       </c>
     </row>
   </sheetData>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>342568.19</v>
+        <v>331574.72</v>
       </c>
     </row>
     <row r="6">
@@ -5168,7 +5168,7 @@
         <v>2462324.51</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1862952.14</v>
+        <v>1851958.67</v>
       </c>
     </row>
     <row r="9">
@@ -5193,452 +5193,452 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
+          <t>Margin Loan 保证金借款</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>16585.31</v>
+        <v>780549.16</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>19605.65</v>
+        <v>936053.71</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>17144.36</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>16386.64</v>
+        <v>613612.8100000001</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>758436.1</v>
+        <v>1609814.63</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>911521.11</v>
+        <v>1916336.22</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>599734.97</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>1470830.81</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>819331.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1604286.88</v>
+        <v>1111711.73</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1911409.27</v>
+        <v>1108417.28</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1474097.33</v>
+        <v>991493.7</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>835718.48</v>
+        <v>1032626.83</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>1117239.48</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1113344.23</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>988227.1800000001</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>1027233.66</v>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>2.433</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>2.711</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>2.466</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>1.456</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>2.699</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>2.474</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>1.464</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>0.9370000000000001</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>-0.131</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>540988.21</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>601029.5699999999</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>489036.03</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>300799.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
+          <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>540988.21</v>
+        <v>570723.52</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>601029.5699999999</v>
+        <v>507387.71</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>489036.03</v>
+        <v>502457.67</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>300799.46</v>
+        <v>731827.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>576251.27</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>512314.66</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>499191.15</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>726434.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="16" t="n">
+      <c r="B17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="E18" s="16" t="n">
-        <v>0</v>
+      <c r="D17" s="7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>COMBINED — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>COMBINED — 双账户法</t>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1111711.73</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1108417.28</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>991493.7</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>684665.47</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>774722.54</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>750170.13</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>641779.85</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>467628.11</v>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1875675.58</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>2024865.34</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1587962.15</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>684665.47</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>1875675.58</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>2024865.34</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1587962.15</v>
-      </c>
-      <c r="E24" s="4" t="n">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>763963.85</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>916448.0600000001</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>596468.45</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>1111711.73</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1108417.28</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>991493.7</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>684665.47</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="n">
-        <v>1100953.04</v>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>1274695.21</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>946182.3</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>217037.36</v>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>774722.54</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>750170.13</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>641779.85</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>467628.11</v>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>16386.64</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="n">
-        <v>342516.94</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>363174.1</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>346447.33</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>559605.55</v>
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>16386.64</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>342516.94</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>363174.1</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>346447.33</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>559605.55</v>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>829265.47</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>980282.51</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>857218</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>819331.84</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
         <v>829265.47</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="4" t="n">
         <v>980282.51</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="4" t="n">
         <v>857218</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="4" t="n">
         <v>819331.84</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>829265.47</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>980282.51</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>857218</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>819331.84</v>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>16585.31</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>19605.65</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>17144.36</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
-        <v>342516.94</v>
-      </c>
-      <c r="C31" s="13" t="n">
-        <v>363174.1</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>346447.33</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>559605.55</v>
+      <c r="B31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>16386.64</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>0</v>
+      <c r="B32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>331574.72</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
-        <v>1117239.48</v>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>1113344.23</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>988227.1800000001</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>1027233.66</v>
+      <c r="B33" s="4" t="n">
+        <v>1111711.73</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>1108417.28</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>991493.7</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1032626.83</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="n">
+      <c r="B34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>442497.98</v>
+        <v>477185.55</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>445625.43</v>
+        <v>480525.72</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>444894.67</v>
+        <v>479314.8</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>453144.88</v>
+        <v>489253.68</v>
       </c>
     </row>
     <row r="40">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>628620.9399999999</v>
+        <v>663308.51</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>627855.74</v>
+        <v>662756.03</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>624060.09</v>
+        <v>658480.22</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>695218.3100000001</v>
+        <v>731327.11</v>
       </c>
     </row>
     <row r="43">
@@ -5774,452 +5774,452 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="n">
-        <v>1751.44</v>
-      </c>
-      <c r="C44" s="13" t="n">
-        <v>1691.97</v>
-      </c>
-      <c r="D44" s="13" t="n">
-        <v>1742.28</v>
-      </c>
-      <c r="E44" s="13" t="n">
-        <v>2443.89</v>
+          <t>Margin Loan 保证金借款</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>0</v>
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>87572.16</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>84598.34</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>87114.08</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>122194.66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>89323.60000000001</v>
+        <v>575736.35</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>86290.31</v>
+        <v>578157.6899999999</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>88856.36</v>
+        <v>571366.14</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>124638.55</v>
+        <v>609132.45</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>539297.34</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>541565.4300000001</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>535203.73</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>570579.76</v>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>0.393</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0.42</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-0.008</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>-0.008</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>36874.3</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>36107.67</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>35484.63</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>47925.91</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
+          <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>36874.3</v>
+        <v>538862.05</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>36107.67</v>
+        <v>542050.02</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>35484.63</v>
+        <v>535881.51</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>47925.91</v>
+        <v>561206.54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>502423.04</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>505457.76</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>499719.1</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>522653.85</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0</v>
+      <c r="B51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>MRPT — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>MRPT — 双账户法</t>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>96799.36</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>95940</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>90309.06</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>117434.88</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>283143.72</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>287793.64</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>272420.75</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>279623.15</v>
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="n">
-        <v>186344.36</v>
-      </c>
-      <c r="C57" s="13" t="n">
-        <v>191853.64</v>
-      </c>
-      <c r="D57" s="13" t="n">
-        <v>182111.69</v>
-      </c>
-      <c r="E57" s="13" t="n">
-        <v>162188.27</v>
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>96799.36</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>95940</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>90309.06</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>117434.88</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
         <v>96799.36</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C59" s="4" t="n">
         <v>95940</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D59" s="4" t="n">
         <v>90309.06</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E59" s="4" t="n">
         <v>117434.88</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>283143.72</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>287793.64</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>272420.75</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>279623.15</v>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="n">
+        <v>1751.44</v>
+      </c>
+      <c r="C60" s="13" t="n">
+        <v>1691.97</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>1742.28</v>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>2443.89</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="n">
-        <v>256153.62</v>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>253771.79</v>
-      </c>
-      <c r="D61" s="13" t="n">
-        <v>262782.98</v>
-      </c>
-      <c r="E61" s="13" t="n">
-        <v>290956.61</v>
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>1751.44</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>1691.97</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>1742.28</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>2443.89</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>256153.62</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>253771.79</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>262782.98</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>290956.61</v>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="n">
+        <v>87572.16</v>
+      </c>
+      <c r="C62" s="13" t="n">
+        <v>84598.34</v>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>87114.08</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>122194.66</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="n">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n">
         <v>87572.16</v>
       </c>
-      <c r="C63" s="13" t="n">
+      <c r="C63" s="4" t="n">
         <v>84598.34</v>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="4" t="n">
         <v>87114.08</v>
       </c>
-      <c r="E63" s="13" t="n">
+      <c r="E63" s="4" t="n">
         <v>122194.66</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n">
-        <v>87572.16</v>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>84598.34</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>87114.08</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>122194.66</v>
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B65" s="13" t="n">
-        <v>256153.62</v>
-      </c>
-      <c r="C65" s="13" t="n">
-        <v>253771.79</v>
-      </c>
-      <c r="D65" s="13" t="n">
-        <v>262782.98</v>
-      </c>
-      <c r="E65" s="13" t="n">
-        <v>290956.61</v>
+      <c r="B65" s="4" t="n">
+        <v>1751.44</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>1691.97</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>1742.28</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>2443.89</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="11" t="n">
-        <v>0</v>
+      <c r="B66" s="13" t="n">
+        <v>477185.55</v>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>480525.72</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>479314.8</v>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>489253.68</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B67" s="13" t="n">
-        <v>539297.34</v>
-      </c>
-      <c r="C67" s="13" t="n">
-        <v>541565.4300000001</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>535203.73</v>
-      </c>
-      <c r="E67" s="13" t="n">
-        <v>570579.76</v>
+      <c r="B67" s="4" t="n">
+        <v>575736.35</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>578157.6899999999</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>571366.14</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>609132.45</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="7" t="n">
+      <c r="B68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6355,452 +6355,452 @@
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
+          <t>Margin Loan 保证金借款</t>
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>14833.87</v>
+        <v>1257734.7</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>17913.68</v>
+        <v>1416579.43</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>15402.08</v>
+        <v>1092927.61</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>13942.74</v>
+        <v>157678.96</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1200934.08</v>
+        <v>1999428.01</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1357146.55</v>
+        <v>2312263.6</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1044629.64</v>
+        <v>1863031.53</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>110576.69</v>
+        <v>854816.14</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>1957461.26</v>
+        <v>535975.39</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>2270744.4</v>
+        <v>530259.59</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>1830135.64</v>
+        <v>420127.56</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>821656.62</v>
+        <v>423494.38</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="n">
-        <v>577942.14</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>571778.79</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>453023.45</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>456653.9</v>
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>4.703</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>5.327</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>5.398</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>2.986</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B82" s="16" t="n">
-        <v>4.361</v>
-      </c>
-      <c r="C82" s="16" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="D82" s="16" t="n">
-        <v>5.006</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>2.769</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="C82" s="17" t="n">
+        <v>1.949</v>
+      </c>
+      <c r="D82" s="17" t="n">
+        <v>1.732</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>-0.307</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="C83" s="7" t="n">
-        <v>1.807</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>1.606</v>
-      </c>
-      <c r="E83" s="7" t="n">
-        <v>-0.284</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="n">
+        <v>504113.91</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>564921.9</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>453551.4</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>252873.55</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
+          <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>504113.91</v>
-      </c>
-      <c r="C84" s="13" t="n">
-        <v>564921.9</v>
-      </c>
-      <c r="D84" s="13" t="n">
-        <v>453551.4</v>
+        <v>31861.48</v>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>-34662.31</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>-33423.84</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>252873.55</v>
+        <v>170620.83</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="n">
-        <v>73828.23</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>6856.89</v>
-      </c>
-      <c r="D85" s="18" t="n">
-        <v>-527.95</v>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>203780.35</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>0</v>
+      <c r="B85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>MTFS — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>MTFS — 双账户法</t>
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="n">
+        <v>535975.39</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>530259.59</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>420127.56</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>423494.38</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n">
-        <v>407879.06</v>
-      </c>
-      <c r="C90" s="4" t="n">
-        <v>390467.64</v>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>299181.95</v>
-      </c>
-      <c r="E90" s="4" t="n">
-        <v>204867.66</v>
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>0</v>
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="n">
+        <v>1778876.22</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>1928925.34</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>1497653.09</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>567230.59</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="n">
-        <v>1778876.22</v>
-      </c>
-      <c r="C92" s="4" t="n">
-        <v>1928925.34</v>
-      </c>
-      <c r="D92" s="4" t="n">
-        <v>1497653.09</v>
-      </c>
-      <c r="E92" s="4" t="n">
-        <v>567230.59</v>
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="n">
+        <v>1242900.83</v>
+      </c>
+      <c r="C92" s="13" t="n">
+        <v>1398665.75</v>
+      </c>
+      <c r="D92" s="13" t="n">
+        <v>1077525.53</v>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>143736.21</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B93" s="13" t="n">
-        <v>1370997.16</v>
-      </c>
-      <c r="C93" s="13" t="n">
-        <v>1538457.7</v>
-      </c>
-      <c r="D93" s="13" t="n">
-        <v>1198471.14</v>
-      </c>
-      <c r="E93" s="13" t="n">
-        <v>362362.94</v>
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n">
+        <v>535975.39</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>530259.59</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>420127.56</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>423494.38</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="n">
-        <v>407879.06</v>
-      </c>
-      <c r="C94" s="4" t="n">
-        <v>390467.64</v>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>299181.95</v>
-      </c>
-      <c r="E94" s="4" t="n">
-        <v>204867.66</v>
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B95" s="13" t="n">
-        <v>170063.08</v>
-      </c>
-      <c r="C95" s="13" t="n">
-        <v>181311.15</v>
-      </c>
-      <c r="D95" s="13" t="n">
-        <v>153841.5</v>
-      </c>
-      <c r="E95" s="13" t="n">
-        <v>251786.24</v>
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="n">
-        <v>170063.08</v>
-      </c>
-      <c r="C96" s="4" t="n">
-        <v>181311.15</v>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>153841.5</v>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>251786.24</v>
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="n">
+        <v>741693.3100000001</v>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>895684.17</v>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>770103.92</v>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>697137.1800000001</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="n">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n">
         <v>741693.3100000001</v>
       </c>
-      <c r="C97" s="13" t="n">
+      <c r="C97" s="4" t="n">
         <v>895684.17</v>
       </c>
-      <c r="D97" s="13" t="n">
+      <c r="D97" s="4" t="n">
         <v>770103.92</v>
       </c>
-      <c r="E97" s="13" t="n">
+      <c r="E97" s="4" t="n">
         <v>697137.1800000001</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="n">
-        <v>741693.3100000001</v>
-      </c>
-      <c r="C98" s="4" t="n">
-        <v>895684.17</v>
-      </c>
-      <c r="D98" s="4" t="n">
-        <v>770103.92</v>
-      </c>
-      <c r="E98" s="4" t="n">
-        <v>697137.1800000001</v>
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="n">
+        <v>14833.87</v>
+      </c>
+      <c r="C98" s="13" t="n">
+        <v>17913.68</v>
+      </c>
+      <c r="D98" s="13" t="n">
+        <v>15402.08</v>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>13942.74</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B99" s="13" t="n">
-        <v>170063.08</v>
-      </c>
-      <c r="C99" s="13" t="n">
-        <v>181311.15</v>
-      </c>
-      <c r="D99" s="13" t="n">
-        <v>153841.5</v>
-      </c>
-      <c r="E99" s="13" t="n">
-        <v>251786.24</v>
+      <c r="B99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B100" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" s="11" t="n">
+      <c r="B100" s="15" t="n">
         <v>-0</v>
       </c>
-      <c r="D100" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="11" t="n">
+      <c r="C100" s="15" t="n">
         <v>-0</v>
       </c>
+      <c r="D100" s="15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="14" t="inlineStr">
+      <c r="A101" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B101" s="13" t="n">
-        <v>577942.14</v>
-      </c>
-      <c r="C101" s="13" t="n">
-        <v>571778.79</v>
-      </c>
-      <c r="D101" s="13" t="n">
-        <v>453023.45</v>
-      </c>
-      <c r="E101" s="13" t="n">
-        <v>456653.9</v>
+      <c r="B101" s="4" t="n">
+        <v>535975.39</v>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>530259.59</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>420127.56</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>423494.38</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="7" t="n">
+      <c r="B102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6870,22 +6870,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3895.25</v>
+        <v>3294.45</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>129012.3</v>
+        <v>120218.03</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>90005.82000000001</v>
+        <v>79084.89999999999</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>195740.69</v>
+        <v>190212.94</v>
       </c>
     </row>
     <row r="6">
@@ -6895,16 +6895,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>103.9</v>
+        <v>106.92</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>519.48</v>
+        <v>534.62</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>2181.8</v>
+        <v>2245.42</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>15376.51</v>
+        <v>15824.83</v>
       </c>
     </row>
     <row r="7">
@@ -6952,22 +6952,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
-        <v>-2268.09</v>
+      <c r="B11" s="19" t="n">
+        <v>-2421.34</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4093.61</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>-31282.42</v>
+        <v>4370.21</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>-33396.1</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>29965.4</v>
+        <v>66404.41</v>
       </c>
     </row>
     <row r="12">
@@ -6976,16 +6976,16 @@
           <t>Interest expense (est)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17" t="n">
+      <c r="B12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7034,22 +7034,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>6163.35</v>
+        <v>5715.8</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>124918.69</v>
+        <v>115847.83</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>121288.24</v>
+        <v>112481.01</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>165775.29</v>
+        <v>123808.54</v>
       </c>
     </row>
     <row r="18">
@@ -7059,16 +7059,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>164.51</v>
+        <v>172.29</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>822.5599999999999</v>
+        <v>861.46</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>3454.74</v>
+        <v>3618.14</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>24347.7</v>
+        <v>25499.28</v>
       </c>
     </row>
     <row r="19">
@@ -7154,19 +7154,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1113344.23</v>
+        <v>1108417.28</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>988227.1800000001</v>
+        <v>991493.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1027233.66</v>
+        <v>1032626.83</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -7179,16 +7179,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>3895.25</v>
+        <v>3294.45</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>129012.3</v>
+        <v>120218.03</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>90005.82000000001</v>
+        <v>79084.89999999999</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>195740.69</v>
+        <v>190212.94</v>
       </c>
     </row>
     <row r="7">
@@ -7216,36 +7216,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="17" t="n">
+      <c r="B8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1117239.48</v>
+        <v>1111711.73</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1117239.48</v>
+        <v>1111711.73</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1117239.48</v>
+        <v>1111711.73</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1117239.48</v>
+        <v>1111711.73</v>
       </c>
     </row>
     <row r="10">
@@ -7254,17 +7254,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>21.24</v>
+      <c r="B10" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>20.64</v>
       </c>
     </row>
     <row r="11">
@@ -7273,17 +7273,17 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-9.57</v>
+      <c r="B11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -7321,19 +7321,19 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>541565.4300000001</v>
+        <v>578157.6899999999</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>535203.73</v>
+        <v>571366.14</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>570579.76</v>
+        <v>609132.45</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -7345,17 +7345,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
-        <v>-2268.09</v>
+      <c r="B16" s="18" t="n">
+        <v>-2421.34</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4093.61</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>-31282.42</v>
+        <v>4370.21</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>-33396.1</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>29965.4</v>
+        <v>66404.41</v>
       </c>
     </row>
     <row r="17">
@@ -7383,36 +7383,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="17" t="n">
+      <c r="B18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>539297.34</v>
+        <v>575736.35</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>539297.34</v>
+        <v>575736.35</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>539297.34</v>
+        <v>575736.35</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>539297.34</v>
+        <v>575736.35</v>
       </c>
     </row>
     <row r="20">
@@ -7424,14 +7424,14 @@
       <c r="B20" s="23" t="n">
         <v>-0.42</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="20" t="n">
         <v>0.76</v>
       </c>
       <c r="D20" s="23" t="n">
         <v>-5.48</v>
       </c>
-      <c r="E20" s="19" t="n">
-        <v>5.88</v>
+      <c r="E20" s="20" t="n">
+        <v>13.04</v>
       </c>
     </row>
     <row r="21">
@@ -7440,17 +7440,17 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="22" t="n">
         <v>-0.42</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="22" t="n">
         <v>-0.44</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="22" t="n">
         <v>-7.18</v>
       </c>
-      <c r="E21" s="21" t="n">
-        <v>-11.94</v>
+      <c r="E21" s="22" t="n">
+        <v>-9.550000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -7488,19 +7488,19 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>571778.79</v>
+        <v>530259.59</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>453023.45</v>
+        <v>420127.56</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>456653.9</v>
+        <v>423494.38</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -7513,16 +7513,16 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>6163.35</v>
+        <v>5715.8</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>124918.69</v>
+        <v>115847.83</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>121288.24</v>
+        <v>112481.01</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>165775.29</v>
+        <v>123808.54</v>
       </c>
     </row>
     <row r="27">
@@ -7550,36 +7550,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="17" t="n">
+      <c r="B28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>577942.14</v>
+        <v>535975.39</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>577942.14</v>
+        <v>535975.39</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>577942.14</v>
+        <v>535975.39</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>577942.14</v>
+        <v>535975.39</v>
       </c>
     </row>
     <row r="30">
@@ -7588,17 +7588,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n">
+      <c r="B30" s="20" t="n">
         <v>1.08</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="20" t="n">
         <v>27.57</v>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D30" s="20" t="n">
         <v>26.56</v>
       </c>
-      <c r="E30" s="19" t="n">
-        <v>40.22</v>
+      <c r="E30" s="20" t="n">
+        <v>30.04</v>
       </c>
     </row>
     <row r="31">
@@ -7607,16 +7607,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="21" t="n">
+      <c r="B31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="22" t="n">
         <v>-1.45</v>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="22" t="n">
         <v>-7.46</v>
       </c>
-      <c r="E31" s="21" t="n">
+      <c r="E31" s="22" t="n">
         <v>-16.75</v>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>129012.3</v>
+        <v>120218.03</v>
       </c>
     </row>
     <row r="5">
@@ -7676,7 +7676,7 @@
           <t>Investing cash flow</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="19" t="n">
         <v>-315665.96</v>
       </c>
     </row>
@@ -7687,7 +7687,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>158701.13</v>
+        <v>166936.35</v>
       </c>
     </row>
     <row r="7">
@@ -7696,8 +7696,8 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
-        <v>-27952.53</v>
+      <c r="B7" s="19" t="n">
+        <v>-28511.58</v>
       </c>
     </row>
     <row r="8">
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1010644.67</v>
+        <v>1011218.51</v>
       </c>
     </row>
     <row r="97">
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1023628.6</v>
+        <v>1025407</v>
       </c>
     </row>
     <row r="98">
@@ -8714,7 +8714,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1025688.39</v>
+        <v>1026941.31</v>
       </c>
     </row>
     <row r="99">
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015764.47</v>
+        <v>1015258.85</v>
       </c>
     </row>
     <row r="100">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1003800.03</v>
+        <v>1003003.03</v>
       </c>
     </row>
     <row r="101">
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1014116.13</v>
+        <v>1013068.4</v>
       </c>
     </row>
     <row r="102">
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1028433.62</v>
+        <v>1026667.89</v>
       </c>
     </row>
     <row r="103">
@@ -8764,7 +8764,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1057149.4</v>
+        <v>1053397.75</v>
       </c>
     </row>
     <row r="104">
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1054547.03</v>
+        <v>1050736.08</v>
       </c>
     </row>
     <row r="105">
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1052398.42</v>
+        <v>1049499.07</v>
       </c>
     </row>
     <row r="106">
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1051419.89</v>
+        <v>1049134.93</v>
       </c>
     </row>
     <row r="107">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1044525.65</v>
+        <v>1042919.9</v>
       </c>
     </row>
     <row r="108">
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1050383.62</v>
+        <v>1048685.92</v>
       </c>
     </row>
     <row r="109">
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1044492.01</v>
+        <v>1042773.4</v>
       </c>
     </row>
     <row r="110">
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1046233.36</v>
+        <v>1044235.83</v>
       </c>
     </row>
     <row r="111">
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1072268.27</v>
+        <v>1070354.14</v>
       </c>
     </row>
     <row r="112">
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1063075.19</v>
+        <v>1061514.84</v>
       </c>
     </row>
     <row r="113">
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1075184.55</v>
+        <v>1074870.62</v>
       </c>
     </row>
     <row r="114">
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080198.27</v>
+        <v>1080512.52</v>
       </c>
     </row>
     <row r="115">
@@ -8884,7 +8884,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1085880.96</v>
+        <v>1086924.48</v>
       </c>
     </row>
     <row r="116">
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1072342.09</v>
+        <v>1071780.32</v>
       </c>
     </row>
     <row r="117">
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065407.09</v>
+        <v>1065526.09</v>
       </c>
     </row>
     <row r="118">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1079521.63</v>
+        <v>1080594.32</v>
       </c>
     </row>
     <row r="119">
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1073799.13</v>
+        <v>1075591.99</v>
       </c>
     </row>
     <row r="120">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1068862.34</v>
+        <v>1071013.67</v>
       </c>
     </row>
     <row r="121">
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1070983.85</v>
+        <v>1073689.47</v>
       </c>
     </row>
     <row r="122">
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1071573.86</v>
+        <v>1074236.64</v>
       </c>
     </row>
     <row r="123">
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1081523.09</v>
+        <v>1084547.15</v>
       </c>
     </row>
     <row r="124">
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1082581.14</v>
+        <v>1085528.37</v>
       </c>
     </row>
     <row r="125">
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1089658.99</v>
+        <v>1092616.33</v>
       </c>
     </row>
     <row r="126">
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1089621.59</v>
+        <v>1092781.06</v>
       </c>
     </row>
     <row r="127">
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1047088.88</v>
+        <v>1053336.82</v>
       </c>
     </row>
     <row r="128">
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1043573.16</v>
+        <v>1049687.33</v>
       </c>
     </row>
     <row r="129">
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1038358.08</v>
+        <v>1044100.12</v>
       </c>
     </row>
     <row r="130">
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1027233.66</v>
+        <v>1032626.83</v>
       </c>
     </row>
     <row r="131">
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1034651.69</v>
+        <v>1039700.39</v>
       </c>
     </row>
     <row r="132">
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1032770.9</v>
+        <v>1037551.62</v>
       </c>
     </row>
     <row r="133">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1015213.94</v>
+        <v>1019311.74</v>
       </c>
     </row>
     <row r="134">
@@ -9074,7 +9074,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1010843.04</v>
+        <v>1014163.76</v>
       </c>
     </row>
     <row r="135">
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>996795.4399999999</v>
+        <v>999293.04</v>
       </c>
     </row>
     <row r="136">
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1007958.56</v>
+        <v>1011409.78</v>
       </c>
     </row>
     <row r="137">
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1010798.69</v>
+        <v>1014540.8</v>
       </c>
     </row>
     <row r="138">
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1008164.48</v>
+        <v>1011881.11</v>
       </c>
     </row>
     <row r="139">
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>995085.9</v>
+        <v>998415.39</v>
       </c>
     </row>
     <row r="140">
@@ -9134,7 +9134,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1012253.33</v>
+        <v>1014351.76</v>
       </c>
     </row>
     <row r="141">
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1021108.83</v>
+        <v>1023498.77</v>
       </c>
     </row>
     <row r="142">
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1021967.79</v>
+        <v>1023696.66</v>
       </c>
     </row>
     <row r="143">
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>993513.08</v>
+        <v>996887.45</v>
       </c>
     </row>
     <row r="144">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1015582.37</v>
+        <v>1016573.57</v>
       </c>
     </row>
     <row r="145">
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>995741.4399999999</v>
+        <v>997861.24</v>
       </c>
     </row>
     <row r="146">
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>988227.1800000001</v>
+        <v>991493.7</v>
       </c>
     </row>
     <row r="147">
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>985354.85</v>
+        <v>989347.35</v>
       </c>
     </row>
     <row r="148">
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1001706.15</v>
+        <v>1004898.62</v>
       </c>
     </row>
     <row r="149">
@@ -9224,7 +9224,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>1103986.9</v>
+        <v>1099657.36</v>
       </c>
     </row>
     <row r="150">
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>1113344.23</v>
+        <v>1108417.28</v>
       </c>
     </row>
     <row r="151">
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="B151" s="13" t="n">
-        <v>1117239.48</v>
+        <v>1111711.73</v>
       </c>
     </row>
   </sheetData>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1117239.48</v>
+        <v>1111711.73</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1875675.58</v>
@@ -9364,16 +9364,16 @@
         <v>1046410.11</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.421</v>
+        <v>2.433</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>242.11</v>
+        <v>243.31</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>121.05</v>
+        <v>121.66</v>
       </c>
       <c r="K4" s="24" t="n">
         <v>15</v>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>539297.34</v>
+        <v>575736.35</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>96799.36</v>
@@ -9401,16 +9401,16 @@
         <v>9227.200000000001</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>0.342</v>
+        <v>0.32</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>34.19</v>
+        <v>32.02</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>17.09</v>
+        <v>16.01</v>
       </c>
       <c r="K5" s="26" t="n">
         <v>1</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>577942.14</v>
+        <v>535975.39</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1778876.22</v>
@@ -9438,16 +9438,16 @@
         <v>1037182.91</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4.361</v>
+        <v>4.703</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1.795</v>
+        <v>1.935</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>436.13</v>
+        <v>470.28</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>218.06</v>
+        <v>235.14</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>14</v>
@@ -9536,10 +9536,10 @@
       <c r="C6" s="4" t="n">
         <v>363427.54</v>
       </c>
-      <c r="D6" s="20" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="E6" s="20" t="n">
+      <c r="D6" s="21" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="E6" s="21" t="n">
         <v>13.44</v>
       </c>
       <c r="F6" s="24" t="n">
@@ -9558,10 +9558,10 @@
       <c r="C7" s="13" t="n">
         <v>289985.42</v>
       </c>
-      <c r="D7" s="19" t="n">
-        <v>25.96</v>
-      </c>
-      <c r="E7" s="19" t="n">
+      <c r="D7" s="20" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="E7" s="20" t="n">
         <v>10.72</v>
       </c>
       <c r="F7" s="26" t="n">
@@ -9580,10 +9580,10 @@
       <c r="C8" s="4" t="n">
         <v>277957.4</v>
       </c>
-      <c r="D8" s="20" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="E8" s="20" t="n">
+      <c r="D8" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" s="21" t="n">
         <v>10.28</v>
       </c>
       <c r="F8" s="24" t="n">
@@ -9602,10 +9602,10 @@
       <c r="C9" s="13" t="n">
         <v>237120</v>
       </c>
-      <c r="D9" s="19" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="E9" s="19" t="n">
+      <c r="D9" s="20" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="E9" s="20" t="n">
         <v>8.77</v>
       </c>
       <c r="F9" s="26" t="n">
@@ -9624,10 +9624,10 @@
       <c r="C10" s="4" t="n">
         <v>232289.9</v>
       </c>
-      <c r="D10" s="20" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="E10" s="20" t="n">
+      <c r="D10" s="21" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="E10" s="21" t="n">
         <v>8.59</v>
       </c>
       <c r="F10" s="24" t="n">
@@ -9646,10 +9646,10 @@
       <c r="C11" s="13" t="n">
         <v>174089.16</v>
       </c>
-      <c r="D11" s="19" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="E11" s="19" t="n">
+      <c r="D11" s="20" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="E11" s="20" t="n">
         <v>6.44</v>
       </c>
       <c r="F11" s="26" t="n">
@@ -9668,10 +9668,10 @@
       <c r="C12" s="4" t="n">
         <v>172580.24</v>
       </c>
-      <c r="D12" s="20" t="n">
-        <v>15.45</v>
-      </c>
-      <c r="E12" s="20" t="n">
+      <c r="D12" s="21" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="E12" s="21" t="n">
         <v>6.38</v>
       </c>
       <c r="F12" s="24" t="n">
@@ -9687,13 +9687,13 @@
       <c r="B13" s="13" t="n">
         <v>137787.24</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="18" t="n">
         <v>-137787.24</v>
       </c>
-      <c r="D13" s="19" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="E13" s="19" t="n">
+      <c r="D13" s="20" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="E13" s="20" t="n">
         <v>5.09</v>
       </c>
       <c r="F13" s="26" t="n">
@@ -9712,10 +9712,10 @@
       <c r="C14" s="4" t="n">
         <v>96799.36</v>
       </c>
-      <c r="D14" s="20" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="E14" s="20" t="n">
+      <c r="D14" s="21" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="E14" s="21" t="n">
         <v>3.58</v>
       </c>
       <c r="F14" s="24" t="n">
@@ -9731,13 +9731,13 @@
       <c r="B15" s="13" t="n">
         <v>87572.16</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="18" t="n">
         <v>-87572.16</v>
       </c>
-      <c r="D15" s="19" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="E15" s="19" t="n">
+      <c r="D15" s="20" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="E15" s="20" t="n">
         <v>3.24</v>
       </c>
       <c r="F15" s="26" t="n">
@@ -9806,13 +9806,13 @@
       <c r="B21" s="13" t="n">
         <v>450537.64</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="13" t="n">
         <v>450537.64</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>16.66</v>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       <c r="C22" s="4" t="n">
         <v>468166.2</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="19" t="n">
         <v>-371366.84</v>
       </c>
       <c r="E22" s="7" t="n">
@@ -9850,7 +9850,7 @@
       <c r="D23" s="13" t="n">
         <v>342427.76</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>12.66</v>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
       <c r="C24" s="4" t="n">
         <v>131733.62</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="19" t="n">
         <v>-131733.62</v>
       </c>
       <c r="E24" s="7" t="n">
@@ -9879,16 +9879,16 @@
           <t>finance</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="15" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>101275.31</v>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="18" t="n">
         <v>-101275.31</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>-3.74</v>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1.706</v>
+        <v>1.715</v>
       </c>
     </row>
     <row r="4">
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>2.416</v>
+        <v>2.428</v>
       </c>
     </row>
     <row r="5">
@@ -9947,7 +9947,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>92.83</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="6">
@@ -9987,7 +9987,7 @@
           <t>tech</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="n">
         <v>31.71</v>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
           <t>materials</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="20" t="n">
         <v>16.66</v>
       </c>
     </row>
@@ -10007,7 +10007,7 @@
           <t>health</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="22" t="n">
         <v>-13.73</v>
       </c>
     </row>
@@ -10017,7 +10017,7 @@
           <t>industrial</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
+      <c r="B13" s="20" t="n">
         <v>12.66</v>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
           <t>food</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="22" t="n">
         <v>-4.87</v>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260605_032615.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260605_032615.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-04  ·  Generated 2026-06-10T09:47:35  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-04  ·  Generated 2026-06-24T18:50:24  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2.433</v>
+        <v>4.313</v>
       </c>
     </row>
     <row r="6">
@@ -758,8 +758,8 @@
           <t>Net leverage (x)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>0.9409999999999999</v>
+      <c r="B6" s="5" t="n">
+        <v>2.821</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1.715</v>
+        <v>5.661</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>35872.22</v>
+        <v>110097.87</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3.23</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>31.14</v>
+        <v>95.56</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.911</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="12">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.9617</v>
+        <v>0.9616</v>
       </c>
     </row>
     <row r="13">
@@ -840,7 +840,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>9.23 / 4.62</t>
+          <t>9.22 / 4.61</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2.433</v>
+        <v>4.313</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BWA (32.69% NAV)</t>
+          <t>KLAC (208.92% NAV)</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>31.71</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="18">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>35872.22</v>
+        <v>110097.87</v>
       </c>
     </row>
     <row r="4">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>50722.67</v>
+        <v>155676.39</v>
       </c>
     </row>
     <row r="5">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>346172.59</v>
+        <v>1062461.74</v>
       </c>
     </row>
     <row r="6">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>31.14</v>
+        <v>95.56</v>
       </c>
     </row>
     <row r="7">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>25083.94</v>
+        <v>82515.45</v>
       </c>
     </row>
     <row r="8">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>27338.16</v>
+        <v>98940.97</v>
       </c>
     </row>
     <row r="10">
@@ -1024,131 +1024,131 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5934.86</v>
+        <v>53786.48</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>16.54</v>
+        <v>48.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>4849.71</v>
+        <v>33071.53</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>13.52</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>4030.45</v>
+        <v>5705.57</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>11.24</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>3174.89</v>
+        <v>4908.09</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>8.85</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2779.91</v>
+        <v>1960.48</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>7.75</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>2093.34</v>
+        <v>1867.13</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>5.84</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1945.06</v>
+        <v>1533.1</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>5.42</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1889.21</v>
+        <v>1509.28</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>5.27</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1725.48</v>
+        <v>1468.6</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>4.81</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1692.57</v>
+        <v>1266.66</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>4.72</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="22">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1629.86</v>
+        <v>1034.59</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>4.54</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1171,49 +1171,49 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1590.19</v>
+        <v>656.51</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>4.43</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1289.97</v>
+        <v>465.94</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>3.6</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>ODFL/JKHY</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>763.01</v>
+        <v>436.83</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>2.13</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>ODFL/JKHY</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>483.7</v>
+        <v>427.07</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1.35</v>
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -1376,8 +1376,8 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>67</v>
+      <c r="C10" s="4" t="n">
+        <v>670</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>989366</v>
@@ -1418,8 +1418,8 @@
           <t>KLAC/LOW</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>42</v>
+      <c r="C12" s="4" t="n">
+        <v>420</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>989366</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-95329.28</v>
+        <v>-314714.71</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>-8.58</v>
+        <v>-28.31</v>
       </c>
     </row>
     <row r="5">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-190658.56</v>
+        <v>-629429.42</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>-17.15</v>
+        <v>-56.61</v>
       </c>
     </row>
     <row r="6">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-95329.28</v>
+        <v>-314714.71</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>-8.58</v>
+        <v>-28.31</v>
       </c>
     </row>
     <row r="7">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-85782.05</v>
+        <v>-294842.96</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>-7.72</v>
+        <v>-26.52</v>
       </c>
     </row>
   </sheetData>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>4.7</v>
+        <v>8.58</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>3</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>1.94</v>
+        <v>5.82</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1870,11 +1870,11 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>32.69</v>
+        <v>208.92</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -1896,11 +1896,11 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>26.08</v>
+        <v>32.69</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1922,11 +1922,11 @@
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>25</v>
+        <v>26.08</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>15</v>
@@ -1941,54 +1941,54 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>sector_net</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="C11" s="34" t="n">
-        <v>31.71</v>
-      </c>
-      <c r="D11" s="34" t="n">
+      <c r="C11" s="32" t="n">
+        <v>61.48</v>
+      </c>
+      <c r="D11" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="34" t="n">
+      <c r="E11" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="34" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>max_pair</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>max_pair</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="D12" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="F12" s="30" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1.72</v>
+        <v>5.66</v>
       </c>
       <c r="D13" s="32" t="n">
         <v>0.3</v>
@@ -2019,28 +2019,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>var_95_1d</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C14" s="34" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="D14" s="34" t="n">
+      <c r="C14" s="32" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D14" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E14" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="34" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -2378,13 +2378,13 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>67</v>
+        <v>670</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>2131.1</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>142783.7</v>
+        <v>1427837</v>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>42</v>
+        <v>420</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>2131.1</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>89506.2</v>
+        <v>895062</v>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>8156.04</v>
+        <v>1293209.34</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>157244.49</v>
+        <v>1442297.79</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12514.72</v>
+        <v>818070.52</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>168782.66</v>
+        <v>974338.46</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>1</v>
@@ -4228,16 +4228,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>14.42</v>
+        <v>14.74</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-0.65</v>
+        <v>-0.49</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>-15.08</v>
+        <v>-15.23</v>
       </c>
     </row>
     <row r="7">
@@ -4247,16 +4247,16 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>13.43</v>
+        <v>13.78</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>11.37</v>
+        <v>15.77</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="23" t="n">
-        <v>-2.06</v>
+      <c r="E7" s="20" t="n">
+        <v>1.99</v>
       </c>
     </row>
     <row r="8">
@@ -4266,16 +4266,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24.38</v>
+        <v>24.95</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.54</v>
+        <v>4.41</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>-20.84</v>
+        <v>-20.54</v>
       </c>
     </row>
     <row r="9">
@@ -4285,16 +4285,16 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>47.76</v>
+        <v>46.53</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>85.73</v>
+        <v>80.31</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>37.97</v>
+        <v>33.79</v>
       </c>
     </row>
     <row r="11">
@@ -4319,101 +4319,101 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>16.54</v>
+        <v>48.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>13.52</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>11.24</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>8.85</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>7.75</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>5.84</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>5.42</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>5.27</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>4.81</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>4.72</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="23">
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>4.54</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -4433,37 +4433,37 @@
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>4.43</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>3.6</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>ODFL/JKHY</t>
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>2.13</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>ODFL/JKHY</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>1.35</v>
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2.6</v>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.111 (t=-0.62)</t>
+          <t>-0.11 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="B6" s="20" t="n">
-        <v>48.07</v>
+        <v>47.74</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>0.059</v>
@@ -4636,27 +4636,27 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>0.056 (t=0.39)</t>
+          <t>0.059 (t=0.41)</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>-0.116 (t=-0.52)</t>
+          <t>-0.119 (t=-0.54)</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>-0.06 (t=-0.31)</t>
+          <t>-0.059 (t=-0.3)</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>0.241 (t=1.31)</t>
+          <t>0.244 (t=1.32)</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>-0.207 (t=-0.72)</t>
+          <t>-0.208 (t=-0.72)</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>28.62</v>
+        <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1.03</v>
@@ -4685,32 +4685,32 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.069 (t=-0.42)</t>
+          <t>-0.073 (t=-0.44)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>-0.004 (t=-0.02)</t>
+          <t>0.001 (t=0.0)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.235 (t=1.04)</t>
+          <t>0.234 (t=1.03)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.103 (t=-0.49)</t>
+          <t>-0.106 (t=-0.5)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.022 (t=0.07)</t>
+          <t>0.023 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.065 (t=-0.55)</t>
+          <t>-0.064 (t=-0.53)</t>
         </is>
       </c>
     </row>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>3.742</v>
+        <v>3.753</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>32.777</v>
+        <v>32.903</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -4811,10 +4811,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1.693</v>
+        <v>1.695</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1.693</v>
+        <v>1.695</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>-0.406</v>
+        <v>-0.444</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>2.324</v>
+        <v>2.457</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>0</v>
@@ -4839,13 +4839,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>1.594</v>
+        <v>1.602</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>1.661</v>
+        <v>1.677</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.067</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="6">
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5.37</v>
+        <v>5.354</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>49.703</v>
+        <v>49.32</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -4867,10 +4867,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>3.745</v>
+        <v>3.752</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>3.745</v>
+        <v>3.752</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.911</v>
+        <v>1.91</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.9617</v>
+        <v>0.9616</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>127</v>
@@ -4953,13 +4953,13 @@
         <v>75.7</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>2.433</v>
+        <v>4.313</v>
       </c>
     </row>
     <row r="10">
@@ -4969,13 +4969,13 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>1.375</v>
+        <v>1.351</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8427</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>8.65</v>
@@ -4987,13 +4987,13 @@
         <v>76.40000000000001</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>6.57</v>
+        <v>6.41</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="11">
@@ -5003,13 +5003,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1.357</v>
+        <v>1.365</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.9026</v>
+        <v>0.904</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.04</v>
@@ -5021,13 +5021,13 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>4.703</v>
+        <v>8.584</v>
       </c>
     </row>
   </sheetData>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>331574.72</v>
+        <v>331420.63</v>
       </c>
     </row>
     <row r="6">
@@ -5140,13 +5140,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1875675.58</v>
+        <v>3966284.68</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2024865.34</v>
+        <v>4031206.54</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1587962.15</v>
+        <v>3948333.29</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>684665.47</v>
@@ -5159,16 +5159,16 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>2721526.36</v>
+        <v>4812135.46</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>3024753.5</v>
+        <v>5031094.7</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2462324.51</v>
+        <v>4822695.65</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1851958.67</v>
+        <v>1851804.58</v>
       </c>
     </row>
     <row r="9">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>780549.16</v>
+        <v>2871000.32</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>936053.71</v>
+        <v>2942254.14</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>613612.8100000001</v>
+        <v>2974077.28</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -5216,13 +5216,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1609814.63</v>
+        <v>3700265.79</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1916336.22</v>
+        <v>3922536.65</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1470830.81</v>
+        <v>3831295.28</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>819331.84</v>
@@ -5235,16 +5235,16 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1032626.83</v>
+        <v>1032472.74</v>
       </c>
     </row>
     <row r="13">
@@ -5254,16 +5254,16 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>2.433</v>
+        <v>4.313</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>2.711</v>
+        <v>4.521</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2.466</v>
+        <v>4.847</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1.456</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="14">
@@ -5273,13 +5273,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.9409999999999999</v>
+        <v>2.821</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.9419999999999999</v>
+        <v>2.752</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>0.737</v>
+        <v>3.118</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>-0.13</v>
@@ -5292,13 +5292,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>540988.21</v>
+        <v>959110.03</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>601029.5699999999</v>
+        <v>1002297.81</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>489036.03</v>
+        <v>961110.26</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>300799.46</v>
@@ -5311,16 +5311,16 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>570723.52</v>
+        <v>152759.64</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>507387.71</v>
+        <v>106260.24</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>502457.67</v>
+        <v>30290.11</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>731827.37</v>
+        <v>731673.28</v>
       </c>
     </row>
     <row r="17">
@@ -5333,10 +5333,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>684665.47</v>
@@ -5421,13 +5421,13 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1875675.58</v>
+        <v>3966284.68</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2024865.34</v>
+        <v>4031206.54</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1587962.15</v>
+        <v>3948333.29</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>684665.47</v>
@@ -5440,13 +5440,13 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>763963.85</v>
+        <v>2854415.01</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>916448.0600000001</v>
+        <v>2922648.49</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>596468.45</v>
+        <v>2956932.92</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -5459,13 +5459,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>684665.47</v>
@@ -5595,13 +5595,13 @@
         <v>0</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>331574.72</v>
+        <v>331420.63</v>
       </c>
     </row>
     <row r="33">
@@ -5611,16 +5611,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1032626.83</v>
+        <v>1032472.74</v>
       </c>
     </row>
     <row r="34">
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>477185.55</v>
+        <v>476144.43</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>480525.72</v>
+        <v>479480.23</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>479314.8</v>
+        <v>478281.59</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>489253.68</v>
+        <v>488152.17</v>
       </c>
     </row>
     <row r="40">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>663308.51</v>
+        <v>662267.39</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>662756.03</v>
+        <v>661710.54</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>658480.22</v>
+        <v>657447.01</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>731327.11</v>
+        <v>730225.6</v>
       </c>
     </row>
     <row r="43">
@@ -5816,16 +5816,16 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>575736.35</v>
+        <v>574695.23</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>578157.6899999999</v>
+        <v>577112.2</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>571366.14</v>
+        <v>570332.9300000001</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>609132.45</v>
+        <v>608030.9399999999</v>
       </c>
     </row>
     <row r="47">
@@ -5835,16 +5835,16 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0.312</v>
+        <v>0.313</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>0.311</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="48">
@@ -5892,16 +5892,16 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>538862.05</v>
+        <v>537820.9300000001</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>542050.02</v>
+        <v>541004.53</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>535881.51</v>
+        <v>534848.3</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>561206.54</v>
+        <v>560105.03</v>
       </c>
     </row>
     <row r="51">
@@ -6173,16 +6173,16 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>477185.55</v>
+        <v>476144.43</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>480525.72</v>
+        <v>479480.23</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>479314.8</v>
+        <v>478281.59</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>489253.68</v>
+        <v>488152.17</v>
       </c>
     </row>
     <row r="67">
@@ -6192,16 +6192,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>575736.35</v>
+        <v>574695.23</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>578157.6899999999</v>
+        <v>577112.2</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>571366.14</v>
+        <v>570332.9300000001</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>609132.45</v>
+        <v>608030.9399999999</v>
       </c>
     </row>
     <row r="68">
@@ -6302,13 +6302,13 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>1778876.22</v>
+        <v>3869485.32</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1928925.34</v>
+        <v>3935266.54</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>1497653.09</v>
+        <v>3858024.23</v>
       </c>
       <c r="E75" s="4" t="n">
         <v>567230.59</v>
@@ -6321,13 +6321,13 @@
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>2535403.4</v>
+        <v>4626012.5</v>
       </c>
       <c r="C76" s="13" t="n">
-        <v>2842523.19</v>
+        <v>4848864.39</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>2283159.09</v>
+        <v>4643530.23</v>
       </c>
       <c r="E76" s="13" t="n">
         <v>1278310.52</v>
@@ -6359,16 +6359,16 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>1257734.7</v>
+        <v>3347144.75</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>1416579.43</v>
+        <v>3421734.37</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>1092927.61</v>
+        <v>3452358.87</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>157678.96</v>
+        <v>156731.55</v>
       </c>
     </row>
     <row r="79">
@@ -6378,16 +6378,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1999428.01</v>
+        <v>4088838.06</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>2312263.6</v>
+        <v>4317418.54</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1863031.53</v>
+        <v>4222462.79</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>854816.14</v>
+        <v>853868.73</v>
       </c>
     </row>
     <row r="80">
@@ -6397,16 +6397,16 @@
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>420127.56</v>
+        <v>421067.44</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>423494.38</v>
+        <v>424441.79</v>
       </c>
     </row>
     <row r="81">
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>4.703</v>
+        <v>8.584</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>5.327</v>
+        <v>9.09</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>5.398</v>
+        <v>10.991</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>2.986</v>
+        <v>2.979</v>
       </c>
     </row>
     <row r="82">
@@ -6435,16 +6435,16 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>1.935</v>
+        <v>5.823</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>1.949</v>
+        <v>5.719</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>1.732</v>
+        <v>7.334</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>-0.307</v>
+        <v>-0.306</v>
       </c>
     </row>
     <row r="83">
@@ -6454,13 +6454,13 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>504113.91</v>
+        <v>922235.73</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>564921.9</v>
+        <v>966190.14</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>453551.4</v>
+        <v>925625.63</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>252873.55</v>
@@ -6472,17 +6472,17 @@
           <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
-      <c r="B84" s="13" t="n">
-        <v>31861.48</v>
+      <c r="B84" s="18" t="n">
+        <v>-385061.29</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>-34662.31</v>
+        <v>-434744.29</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-33423.84</v>
+        <v>-504558.19</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>170620.83</v>
+        <v>171568.24</v>
       </c>
     </row>
     <row r="85">
@@ -6498,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
@@ -6545,16 +6545,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>420127.56</v>
+        <v>421067.44</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>423494.38</v>
+        <v>424441.79</v>
       </c>
     </row>
     <row r="90">
@@ -6583,13 +6583,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>1778876.22</v>
+        <v>3869485.32</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1928925.34</v>
+        <v>3935266.54</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1497653.09</v>
+        <v>3858024.23</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>567230.59</v>
@@ -6602,16 +6602,16 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>1242900.83</v>
+        <v>3332310.88</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>1398665.75</v>
+        <v>3403820.69</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>1077525.53</v>
+        <v>3436956.79</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>143736.21</v>
+        <v>142788.8</v>
       </c>
     </row>
     <row r="93">
@@ -6621,16 +6621,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>420127.56</v>
+        <v>421067.44</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>423494.38</v>
+        <v>424441.79</v>
       </c>
     </row>
     <row r="94">
@@ -6754,13 +6754,13 @@
         </is>
       </c>
       <c r="B100" s="15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C100" s="15" t="n">
         <v>-0</v>
       </c>
       <c r="D100" s="15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E100" s="15" t="n">
         <v>0</v>
@@ -6773,16 +6773,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>420127.56</v>
+        <v>421067.44</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>423494.38</v>
+        <v>424441.79</v>
       </c>
     </row>
     <row r="102">
@@ -6876,16 +6876,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3294.45</v>
+        <v>3311.62</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>120218.03</v>
+        <v>120469.3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>79084.89999999999</v>
+        <v>79396.92999999999</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>190212.94</v>
+        <v>190370.88</v>
       </c>
     </row>
     <row r="6">
@@ -6895,16 +6895,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>106.92</v>
+        <v>393.29</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>534.62</v>
+        <v>1966.44</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>2245.42</v>
+        <v>8259.040000000001</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>15824.83</v>
+        <v>58206.58</v>
       </c>
     </row>
     <row r="7">
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>142827.63</v>
+        <v>2233436.73</v>
       </c>
     </row>
     <row r="9">
@@ -6958,16 +6958,16 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>-2421.34</v>
+        <v>-2416.97</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4370.21</v>
+        <v>4362.3</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>-33396.1</v>
+        <v>-33335.71</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66404.41</v>
+        <v>65363.29</v>
       </c>
     </row>
     <row r="12">
@@ -7040,16 +7040,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>5715.8</v>
+        <v>5728.59</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>115847.83</v>
+        <v>116107</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>112481.01</v>
+        <v>112732.65</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>123808.54</v>
+        <v>125007.59</v>
       </c>
     </row>
     <row r="18">
@@ -7059,16 +7059,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>172.29</v>
+        <v>458.51</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>861.46</v>
+        <v>2292.56</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>3618.14</v>
+        <v>9628.77</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>25499.28</v>
+        <v>67859.92</v>
       </c>
     </row>
     <row r="19">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>131850.05</v>
+        <v>2222459.15</v>
       </c>
     </row>
     <row r="21">
@@ -7160,13 +7160,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1032626.83</v>
+        <v>1032472.74</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -7179,16 +7179,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>3294.45</v>
+        <v>3311.62</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>120218.03</v>
+        <v>120469.3</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>79084.89999999999</v>
+        <v>79396.92999999999</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>190212.94</v>
+        <v>190370.88</v>
       </c>
     </row>
     <row r="7">
@@ -7236,16 +7236,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
     </row>
     <row r="10">
@@ -7258,13 +7258,13 @@
         <v>0.3</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>12.12</v>
+        <v>12.15</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>7.66</v>
+        <v>7.69</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>20.64</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="11">
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>578157.6899999999</v>
+        <v>577112.2</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>571366.14</v>
+        <v>570332.9300000001</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>609132.45</v>
+        <v>608030.9399999999</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -7346,16 +7346,16 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>-2421.34</v>
+        <v>-2416.97</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4370.21</v>
+        <v>4362.3</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>-33396.1</v>
+        <v>-33335.71</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>66404.41</v>
+        <v>65363.29</v>
       </c>
     </row>
     <row r="17">
@@ -7403,16 +7403,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>575736.35</v>
+        <v>574695.23</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>575736.35</v>
+        <v>574695.23</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>575736.35</v>
+        <v>574695.23</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>575736.35</v>
+        <v>574695.23</v>
       </c>
     </row>
     <row r="20">
@@ -7431,7 +7431,7 @@
         <v>-5.48</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>13.04</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="21">
@@ -7494,13 +7494,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>420127.56</v>
+        <v>421067.44</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>423494.38</v>
+        <v>424441.79</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -7513,16 +7513,16 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>5715.8</v>
+        <v>5728.59</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>115847.83</v>
+        <v>116107</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>112481.01</v>
+        <v>112732.65</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>123808.54</v>
+        <v>125007.59</v>
       </c>
     </row>
     <row r="27">
@@ -7570,16 +7570,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
     </row>
     <row r="30">
@@ -7598,7 +7598,7 @@
         <v>26.56</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>30.04</v>
+        <v>30.33</v>
       </c>
     </row>
     <row r="31">
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>120218.03</v>
+        <v>120469.3</v>
       </c>
     </row>
     <row r="5">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-315665.96</v>
+        <v>-45903.92</v>
       </c>
     </row>
     <row r="6">
@@ -7686,8 +7686,8 @@
           <t>Financing cash flow</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>166936.35</v>
+      <c r="B6" s="19" t="n">
+        <v>-103076.96</v>
       </c>
     </row>
     <row r="7">
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1011218.51</v>
+        <v>1011202.12</v>
       </c>
     </row>
     <row r="97">
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1025407</v>
+        <v>1025356.19</v>
       </c>
     </row>
     <row r="98">
@@ -8714,7 +8714,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1026941.31</v>
+        <v>1026905.51</v>
       </c>
     </row>
     <row r="99">
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015258.85</v>
+        <v>1015273.3</v>
       </c>
     </row>
     <row r="100">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1003003.03</v>
+        <v>1003025.8</v>
       </c>
     </row>
     <row r="101">
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1013068.4</v>
+        <v>1013098.34</v>
       </c>
     </row>
     <row r="102">
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1026667.89</v>
+        <v>1026718.34</v>
       </c>
     </row>
     <row r="103">
@@ -8764,7 +8764,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1053397.75</v>
+        <v>1053504.94</v>
       </c>
     </row>
     <row r="104">
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1050736.08</v>
+        <v>1050844.96</v>
       </c>
     </row>
     <row r="105">
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1049499.07</v>
+        <v>1049581.91</v>
       </c>
     </row>
     <row r="106">
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1049134.93</v>
+        <v>1049200.21</v>
       </c>
     </row>
     <row r="107">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1042919.9</v>
+        <v>1042965.78</v>
       </c>
     </row>
     <row r="108">
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1048685.92</v>
+        <v>1048734.43</v>
       </c>
     </row>
     <row r="109">
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1042773.4</v>
+        <v>1042822.5</v>
       </c>
     </row>
     <row r="110">
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1044235.83</v>
+        <v>1044292.9</v>
       </c>
     </row>
     <row r="111">
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1070354.14</v>
+        <v>1070408.83</v>
       </c>
     </row>
     <row r="112">
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1061514.84</v>
+        <v>1061559.43</v>
       </c>
     </row>
     <row r="113">
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1074870.62</v>
+        <v>1074879.59</v>
       </c>
     </row>
     <row r="114">
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080512.52</v>
+        <v>1080503.54</v>
       </c>
     </row>
     <row r="115">
@@ -8884,7 +8884,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1086924.48</v>
+        <v>1086894.67</v>
       </c>
     </row>
     <row r="116">
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1071780.32</v>
+        <v>1071796.37</v>
       </c>
     </row>
     <row r="117">
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065526.09</v>
+        <v>1065522.69</v>
       </c>
     </row>
     <row r="118">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1080594.32</v>
+        <v>1080563.67</v>
       </c>
     </row>
     <row r="119">
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1075591.99</v>
+        <v>1075540.76</v>
       </c>
     </row>
     <row r="120">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1071013.67</v>
+        <v>1070952.2</v>
       </c>
     </row>
     <row r="121">
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1073689.47</v>
+        <v>1073612.17</v>
       </c>
     </row>
     <row r="122">
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1074236.64</v>
+        <v>1074160.56</v>
       </c>
     </row>
     <row r="123">
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1084547.15</v>
+        <v>1084460.75</v>
       </c>
     </row>
     <row r="124">
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1085528.37</v>
+        <v>1085444.17</v>
       </c>
     </row>
     <row r="125">
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1092616.33</v>
+        <v>1092531.84</v>
       </c>
     </row>
     <row r="126">
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1092781.06</v>
+        <v>1092690.79</v>
       </c>
     </row>
     <row r="127">
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1053336.82</v>
+        <v>1053158.31</v>
       </c>
     </row>
     <row r="128">
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1049687.33</v>
+        <v>1049512.64</v>
       </c>
     </row>
     <row r="129">
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1044100.12</v>
+        <v>1043936.06</v>
       </c>
     </row>
     <row r="130">
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1032626.83</v>
+        <v>1032472.74</v>
       </c>
     </row>
     <row r="131">
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1039700.39</v>
+        <v>1039556.14</v>
       </c>
     </row>
     <row r="132">
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1037551.62</v>
+        <v>1037415.03</v>
       </c>
     </row>
     <row r="133">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1019311.74</v>
+        <v>1019194.66</v>
       </c>
     </row>
     <row r="134">
@@ -9074,7 +9074,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1014163.76</v>
+        <v>1014068.88</v>
       </c>
     </row>
     <row r="135">
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>999293.04</v>
+        <v>999221.6800000001</v>
       </c>
     </row>
     <row r="136">
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1011409.78</v>
+        <v>1011311.18</v>
       </c>
     </row>
     <row r="137">
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1014540.8</v>
+        <v>1014433.88</v>
       </c>
     </row>
     <row r="138">
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1011881.11</v>
+        <v>1011774.92</v>
       </c>
     </row>
     <row r="139">
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>998415.39</v>
+        <v>998320.26</v>
       </c>
     </row>
     <row r="140">
@@ -9134,7 +9134,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1014351.76</v>
+        <v>1014291.81</v>
       </c>
     </row>
     <row r="141">
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1023498.77</v>
+        <v>1023430.49</v>
       </c>
     </row>
     <row r="142">
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1023696.66</v>
+        <v>1023647.26</v>
       </c>
     </row>
     <row r="143">
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
     </row>
     <row r="144">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1016573.57</v>
+        <v>1016545.25</v>
       </c>
     </row>
     <row r="145">
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
     </row>
     <row r="146">
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
     </row>
     <row r="147">
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
     </row>
     <row r="148">
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
     </row>
     <row r="149">
@@ -9224,7 +9224,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
     </row>
     <row r="150">
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
     </row>
     <row r="151">
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="B151" s="13" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
     </row>
   </sheetData>
@@ -9349,31 +9349,31 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1875675.58</v>
+        <v>3966284.68</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>829265.47</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2704941.05</v>
+        <v>4795550.15</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1046410.11</v>
+        <v>3137019.21</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.433</v>
+        <v>4.313</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.9409999999999999</v>
+        <v>2.821</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>243.31</v>
+        <v>431.31</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>121.66</v>
+        <v>215.65</v>
       </c>
       <c r="K4" s="24" t="n">
         <v>15</v>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>575736.35</v>
+        <v>574695.23</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>96799.36</v>
@@ -9401,16 +9401,16 @@
         <v>9227.200000000001</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>0.016</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>32.02</v>
+        <v>32.08</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>16.01</v>
+        <v>16.04</v>
       </c>
       <c r="K5" s="26" t="n">
         <v>1</v>
@@ -9423,31 +9423,31 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1778876.22</v>
+        <v>3869485.32</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>741693.3100000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2520569.53</v>
+        <v>4611178.63</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1037182.91</v>
+        <v>3127792.01</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4.703</v>
+        <v>8.584</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1.935</v>
+        <v>5.823</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>470.28</v>
+        <v>858.41</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>235.14</v>
+        <v>429.21</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>14</v>
@@ -9488,7 +9488,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>HHI=0.0723  ·  effective N pairs=13.8  ·  max pair=9.73% of gross</t>
+          <t>HHI=0.1524  ·  effective N pairs=6.6  ·  max pair=30.08% of gross</t>
         </is>
       </c>
     </row>
@@ -9527,20 +9527,20 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>363427.54</v>
+        <v>2322899</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>363427.54</v>
+        <v>2322899</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>32.69</v>
+        <v>208.92</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>13.44</v>
+        <v>48.44</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>2</v>
@@ -9549,20 +9549,20 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>289985.42</v>
+        <v>363427.54</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>289985.42</v>
+        <v>363427.54</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>26.08</v>
+        <v>32.69</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>10.72</v>
+        <v>7.58</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>2</v>
@@ -9571,20 +9571,20 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>277957.4</v>
+        <v>289985.42</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>277957.4</v>
+        <v>289985.42</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>25</v>
+        <v>26.08</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>10.28</v>
+        <v>6.05</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>2</v>
@@ -9593,20 +9593,20 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>237120</v>
+        <v>277957.4</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>237120</v>
+        <v>277957.4</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>21.33</v>
+        <v>25</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>8.77</v>
+        <v>5.8</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>2</v>
@@ -9615,20 +9615,20 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>232289.9</v>
+        <v>237120</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>232289.9</v>
+        <v>237120</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>20.89</v>
+        <v>21.33</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>8.59</v>
+        <v>4.94</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>2</v>
@@ -9650,7 +9650,7 @@
         <v>15.66</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>6.44</v>
+        <v>3.63</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>1</v>
@@ -9672,7 +9672,7 @@
         <v>15.52</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>6.38</v>
+        <v>3.6</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>2</v>
@@ -9694,7 +9694,7 @@
         <v>12.39</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>5.09</v>
+        <v>2.87</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>2</v>
@@ -9716,7 +9716,7 @@
         <v>8.710000000000001</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>3.58</v>
+        <v>2.02</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>1</v>
@@ -9738,7 +9738,7 @@
         <v>7.88</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>3.24</v>
+        <v>1.83</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>1</v>
@@ -9785,16 +9785,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>933484.48</v>
+        <v>3024093.58</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>75664</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>857820.48</v>
+        <v>2948429.58</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>31.71</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="21">
@@ -9813,7 +9813,7 @@
         <v>450537.64</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>16.66</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -9832,7 +9832,7 @@
         <v>-371366.84</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-13.73</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="23">
@@ -9851,7 +9851,7 @@
         <v>342427.76</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>12.66</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="24">
@@ -9870,7 +9870,7 @@
         <v>-131733.62</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-4.87</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="25">
@@ -9889,7 +9889,7 @@
         <v>-101275.31</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>-3.74</v>
+        <v>-2.11</v>
       </c>
     </row>
   </sheetData>
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1.715</v>
+        <v>5.661</v>
       </c>
     </row>
     <row r="4">
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>2.428</v>
+        <v>6.375</v>
       </c>
     </row>
     <row r="5">
@@ -9947,7 +9947,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>93.3</v>
+        <v>281.31</v>
       </c>
     </row>
     <row r="6">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>31.71</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="11">
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>16.66</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>-13.73</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="13">
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="B13" s="20" t="n">
-        <v>12.66</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="14">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>-4.87</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="15">
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>-3.74</v>
+        <v>-2.11</v>
       </c>
     </row>
   </sheetData>

--- a/trading_signals/risk_management/risk_workbook_20260605_032615.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260605_032615.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-04  ·  Generated 2026-06-24T18:50:24  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-04  ·  Generated 2026-06-25T01:17:41  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260605_032615.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260605_032615.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-04  ·  Generated 2026-06-25T01:17:41  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-04  ·  Generated 2026-06-25T01:35:33  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260605_032615.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260605_032615.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-04  ·  Generated 2026-06-25T01:35:33  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-04  ·  Generated 2026-06-25T01:48:57  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>4.313</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="6">
@@ -758,8 +758,8 @@
           <t>Net leverage (x)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>2.821</v>
+      <c r="B6" s="6" t="n">
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5.661</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>110097.87</v>
+        <v>35872.22</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>9.9</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>95.56</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="11">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>4.313</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>KLAC (208.92% NAV)</t>
+          <t>BWA (32.69% NAV)</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>61.48</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="18">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>110097.87</v>
+        <v>35872.22</v>
       </c>
     </row>
     <row r="4">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>155676.39</v>
+        <v>50722.67</v>
       </c>
     </row>
     <row r="5">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1062461.74</v>
+        <v>346172.59</v>
       </c>
     </row>
     <row r="6">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>95.56</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="7">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>82515.45</v>
+        <v>25083.94</v>
       </c>
     </row>
     <row r="8">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>98940.97</v>
+        <v>27338.16</v>
       </c>
     </row>
     <row r="10">
@@ -1024,131 +1024,131 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>53786.48</v>
+        <v>5934.86</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>48.85</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>33071.53</v>
+        <v>4849.71</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>30.04</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>5705.57</v>
+        <v>4030.45</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>5.18</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>4908.09</v>
+        <v>3174.89</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>4.46</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1960.48</v>
+        <v>2779.91</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1.78</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1867.13</v>
+        <v>2093.34</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>1.7</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1533.1</v>
+        <v>1945.06</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1.39</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1509.28</v>
+        <v>1889.21</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1.37</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1468.6</v>
+        <v>1725.48</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1.33</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1266.66</v>
+        <v>1692.57</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1.15</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="22">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1034.59</v>
+        <v>1629.86</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="23">
@@ -1171,49 +1171,49 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>656.51</v>
+        <v>1590.19</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>0.6</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>465.94</v>
+        <v>1289.97</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>0.42</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>ODFL/JKHY</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>436.83</v>
+        <v>763.01</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.4</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>ODFL/JKHY</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>427.07</v>
+        <v>483.7</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>0.39</v>
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1380,7 @@
         <v>670</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>989366</v>
+        <v>9893663</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>420</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>989366</v>
+        <v>9893663</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-314714.71</v>
+        <v>-95287.23</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>-28.31</v>
+        <v>-8.57</v>
       </c>
     </row>
     <row r="5">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-629429.42</v>
+        <v>-190574.46</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>-56.61</v>
+        <v>-17.14</v>
       </c>
     </row>
     <row r="6">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-314714.71</v>
+        <v>-95287.23</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>-28.31</v>
+        <v>-8.57</v>
       </c>
     </row>
     <row r="7">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-294842.96</v>
+        <v>-85782.05</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>-26.52</v>
+        <v>-7.72</v>
       </c>
     </row>
   </sheetData>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>8.58</v>
+        <v>4.69</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>3</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>5.82</v>
+        <v>1.93</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1870,11 +1870,11 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>208.92</v>
+        <v>32.69</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -1896,11 +1896,11 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>32.69</v>
+        <v>26.08</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1922,11 +1922,11 @@
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>26.08</v>
+        <v>25</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>15</v>
@@ -1941,54 +1941,54 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>sector_net</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
-        <v>61.48</v>
-      </c>
-      <c r="D11" s="32" t="n">
+      <c r="C11" s="34" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="D11" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>max_pair</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C12" s="34" t="n">
-        <v>30.08</v>
-      </c>
-      <c r="D12" s="34" t="n">
+      <c r="C12" s="30" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="D12" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="34" t="n">
+      <c r="E12" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="F12" s="34" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5.66</v>
+        <v>1.71</v>
       </c>
       <c r="D13" s="32" t="n">
         <v>0.3</v>
@@ -2019,28 +2019,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>var_95_1d</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="D14" s="32" t="n">
+      <c r="C14" s="34" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="D14" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="32" t="n">
+      <c r="E14" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         <v>670</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2131.1</v>
+        <v>213.11</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>1427837</v>
+        <v>142783.7</v>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
@@ -2469,10 +2469,10 @@
         <v>420</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2131.1</v>
+        <v>213.11</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>895062</v>
+        <v>89506.2</v>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1293209.34</v>
+        <v>8156.04</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1442297.79</v>
+        <v>157244.49</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>818070.52</v>
+        <v>12514.72</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>974338.46</v>
+        <v>168782.66</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>1</v>
@@ -4319,101 +4319,101 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>48.85</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>30.04</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>5.18</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>4.46</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>1.78</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>1.7</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>1.39</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>1.37</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>1.33</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>1.15</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="23">
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="24">
@@ -4433,37 +4433,37 @@
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>0.6</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.42</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>ODFL/JKHY</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>0.4</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>ODFL/JKHY</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.39</v>
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>
@@ -4959,7 +4959,7 @@
         <v>4.61</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>4.313</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="10">
@@ -5027,7 +5027,7 @@
         <v>1.62</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>8.584</v>
+        <v>4.692</v>
       </c>
     </row>
   </sheetData>
@@ -5140,13 +5140,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3966284.68</v>
+        <v>1875675.58</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4031206.54</v>
+        <v>2024865.34</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3948333.29</v>
+        <v>1587962.15</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>684665.47</v>
@@ -5159,13 +5159,13 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>4812135.46</v>
+        <v>2721526.36</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>5031094.7</v>
+        <v>3024753.5</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>4822695.65</v>
+        <v>2462324.51</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>1851804.58</v>
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>2871000.32</v>
+        <v>780391.22</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>2942254.14</v>
+        <v>935912.9399999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2974077.28</v>
+        <v>613706.14</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -5216,13 +5216,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>3700265.79</v>
+        <v>1609656.69</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3922536.65</v>
+        <v>1916195.45</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3831295.28</v>
+        <v>1470924.14</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>819331.84</v>
@@ -5254,13 +5254,13 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4.313</v>
+        <v>2.433</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>4.521</v>
+        <v>2.711</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>4.847</v>
+        <v>2.466</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1.457</v>
@@ -5273,13 +5273,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>2.821</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>2.752</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>3.118</v>
+        <v>0.737</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>-0.13</v>
@@ -5292,13 +5292,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>959110.03</v>
+        <v>540988.21</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1002297.81</v>
+        <v>601029.5699999999</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>961110.26</v>
+        <v>489036.03</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>300799.46</v>
@@ -5311,13 +5311,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>152759.64</v>
+        <v>570881.46</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>106260.24</v>
+        <v>507528.48</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>30290.11</v>
+        <v>502364.34</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>731673.28</v>
@@ -5333,10 +5333,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -5421,13 +5421,13 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>3966284.68</v>
+        <v>1875675.58</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4031206.54</v>
+        <v>2024865.34</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3948333.29</v>
+        <v>1587962.15</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>684665.47</v>
@@ -5440,13 +5440,13 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>2854415.01</v>
+        <v>763805.91</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>2922648.49</v>
+        <v>916307.29</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>2956932.92</v>
+        <v>596561.78</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -5595,10 +5595,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>331420.63</v>
@@ -6302,13 +6302,13 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>3869485.32</v>
+        <v>1778876.22</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>3935266.54</v>
+        <v>1928925.34</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>3858024.23</v>
+        <v>1497653.09</v>
       </c>
       <c r="E75" s="4" t="n">
         <v>567230.59</v>
@@ -6321,13 +6321,13 @@
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>4626012.5</v>
+        <v>2535403.4</v>
       </c>
       <c r="C76" s="13" t="n">
-        <v>4848864.39</v>
+        <v>2842523.19</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>4643530.23</v>
+        <v>2283159.09</v>
       </c>
       <c r="E76" s="13" t="n">
         <v>1278310.52</v>
@@ -6359,13 +6359,13 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>3347144.75</v>
+        <v>1256535.65</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>3421734.37</v>
+        <v>1415393.17</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>3452358.87</v>
+        <v>1091987.73</v>
       </c>
       <c r="E78" s="13" t="n">
         <v>156731.55</v>
@@ -6378,13 +6378,13 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>4088838.06</v>
+        <v>1998228.96</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>4317418.54</v>
+        <v>2311077.34</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>4222462.79</v>
+        <v>1862091.65</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>853868.73</v>
@@ -6416,13 +6416,13 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>8.584</v>
+        <v>4.692</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>9.09</v>
+        <v>5.315</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>10.991</v>
+        <v>5.386</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>2.979</v>
@@ -6435,13 +6435,13 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>5.823</v>
+        <v>1.931</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>5.719</v>
+        <v>1.944</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>7.334</v>
+        <v>1.728</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>-0.306</v>
@@ -6454,13 +6454,13 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>922235.73</v>
+        <v>504113.91</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>966190.14</v>
+        <v>564921.9</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>925625.63</v>
+        <v>453551.4</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>252873.55</v>
@@ -6472,14 +6472,14 @@
           <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
-      <c r="B84" s="18" t="n">
-        <v>-385061.29</v>
+      <c r="B84" s="13" t="n">
+        <v>33060.53</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>-434744.29</v>
+        <v>-33476.05</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-504558.19</v>
+        <v>-32483.96</v>
       </c>
       <c r="E84" s="13" t="n">
         <v>171568.24</v>
@@ -6498,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
@@ -6583,13 +6583,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>3869485.32</v>
+        <v>1778876.22</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>3935266.54</v>
+        <v>1928925.34</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>3858024.23</v>
+        <v>1497653.09</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>567230.59</v>
@@ -6602,13 +6602,13 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>3332310.88</v>
+        <v>1241701.78</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>3403820.69</v>
+        <v>1397479.49</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>3436956.79</v>
+        <v>1076585.65</v>
       </c>
       <c r="E92" s="13" t="n">
         <v>142788.8</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D100" s="15" t="n">
         <v>0</v>
@@ -6895,16 +6895,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>393.29</v>
+        <v>106.9</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1966.44</v>
+        <v>534.51</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>8259.040000000001</v>
+        <v>2244.96</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>58206.58</v>
+        <v>15821.63</v>
       </c>
     </row>
     <row r="7">
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2233436.73</v>
+        <v>142827.63</v>
       </c>
     </row>
     <row r="9">
@@ -7059,16 +7059,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>458.51</v>
+        <v>172.13</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>2292.56</v>
+        <v>860.64</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>9628.77</v>
+        <v>3614.69</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>67859.92</v>
+        <v>25474.97</v>
       </c>
     </row>
     <row r="19">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2222459.15</v>
+        <v>131850.05</v>
       </c>
     </row>
     <row r="21">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-45903.92</v>
+        <v>-315665.96</v>
       </c>
     </row>
     <row r="6">
@@ -7686,8 +7686,8 @@
           <t>Financing cash flow</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>-103076.96</v>
+      <c r="B6" s="4" t="n">
+        <v>166685.08</v>
       </c>
     </row>
     <row r="7">
@@ -9352,28 +9352,28 @@
         <v>1111869.67</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3966284.68</v>
+        <v>1875675.58</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>829265.47</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4795550.15</v>
+        <v>2704941.05</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3137019.21</v>
+        <v>1046410.11</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>4.313</v>
+        <v>2.433</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2.821</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>431.31</v>
+        <v>243.28</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>215.65</v>
+        <v>121.64</v>
       </c>
       <c r="K4" s="24" t="n">
         <v>15</v>
@@ -9426,28 +9426,28 @@
         <v>537174.4399999999</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3869485.32</v>
+        <v>1778876.22</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>741693.3100000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4611178.63</v>
+        <v>2520569.53</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3127792.01</v>
+        <v>1037182.91</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>8.584</v>
+        <v>4.692</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>5.823</v>
+        <v>1.931</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>858.41</v>
+        <v>469.23</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>429.21</v>
+        <v>234.61</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>14</v>
@@ -9488,7 +9488,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>HHI=0.1524  ·  effective N pairs=6.6  ·  max pair=30.08% of gross</t>
+          <t>HHI=0.0723  ·  effective N pairs=13.8  ·  max pair=9.73% of gross</t>
         </is>
       </c>
     </row>
@@ -9527,20 +9527,20 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2322899</v>
+        <v>363427.54</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2322899</v>
+        <v>363427.54</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>208.92</v>
+        <v>32.69</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>48.44</v>
+        <v>13.44</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>2</v>
@@ -9549,20 +9549,20 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>363427.54</v>
+        <v>289985.42</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>363427.54</v>
+        <v>289985.42</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>32.69</v>
+        <v>26.08</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>7.58</v>
+        <v>10.72</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>2</v>
@@ -9571,20 +9571,20 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>289985.42</v>
+        <v>277957.4</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>289985.42</v>
+        <v>277957.4</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>26.08</v>
+        <v>25</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>6.05</v>
+        <v>10.28</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>2</v>
@@ -9593,20 +9593,20 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>277957.4</v>
+        <v>237120</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>277957.4</v>
+        <v>237120</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>25</v>
+        <v>21.33</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>5.8</v>
+        <v>8.77</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>2</v>
@@ -9615,20 +9615,20 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>237120</v>
+        <v>232289.9</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>237120</v>
+        <v>232289.9</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>21.33</v>
+        <v>20.89</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>4.94</v>
+        <v>8.59</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>2</v>
@@ -9650,7 +9650,7 @@
         <v>15.66</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>3.63</v>
+        <v>6.44</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>1</v>
@@ -9672,7 +9672,7 @@
         <v>15.52</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>3.6</v>
+        <v>6.38</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>2</v>
@@ -9694,7 +9694,7 @@
         <v>12.39</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>2.87</v>
+        <v>5.09</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>2</v>
@@ -9716,7 +9716,7 @@
         <v>8.710000000000001</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>2.02</v>
+        <v>3.58</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>1</v>
@@ -9738,7 +9738,7 @@
         <v>7.88</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>1.83</v>
+        <v>3.24</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>1</v>
@@ -9785,16 +9785,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>3024093.58</v>
+        <v>933484.48</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>75664</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2948429.58</v>
+        <v>857820.48</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>61.48</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="21">
@@ -9813,7 +9813,7 @@
         <v>450537.64</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>9.390000000000001</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="22">
@@ -9832,7 +9832,7 @@
         <v>-371366.84</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-7.74</v>
+        <v>-13.73</v>
       </c>
     </row>
     <row r="23">
@@ -9851,7 +9851,7 @@
         <v>342427.76</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>7.14</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="24">
@@ -9870,7 +9870,7 @@
         <v>-131733.62</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-2.75</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="25">
@@ -9889,7 +9889,7 @@
         <v>-101275.31</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>-2.11</v>
+        <v>-3.74</v>
       </c>
     </row>
   </sheetData>
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5.661</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="4">
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>6.375</v>
+        <v>2.428</v>
       </c>
     </row>
     <row r="5">
@@ -9947,7 +9947,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>281.31</v>
+        <v>93.28</v>
       </c>
     </row>
     <row r="6">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>61.48</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="11">
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>9.390000000000001</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="12">
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>-7.74</v>
+        <v>-13.73</v>
       </c>
     </row>
     <row r="13">
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="B13" s="20" t="n">
-        <v>7.14</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="14">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>-2.75</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="15">
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>-2.11</v>
+        <v>-3.74</v>
       </c>
     </row>
   </sheetData>
